--- a/artfynd/A 54167-2025 artfynd.xlsx
+++ b/artfynd/A 54167-2025 artfynd.xlsx
@@ -798,7 +798,7 @@
         <v>130184920</v>
       </c>
       <c r="B3" t="n">
-        <v>80066</v>
+        <v>80151</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>

--- a/artfynd/A 54167-2025 artfynd.xlsx
+++ b/artfynd/A 54167-2025 artfynd.xlsx
@@ -798,7 +798,7 @@
         <v>130184920</v>
       </c>
       <c r="B3" t="n">
-        <v>80151</v>
+        <v>80154</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>

--- a/artfynd/A 54167-2025 artfynd.xlsx
+++ b/artfynd/A 54167-2025 artfynd.xlsx
@@ -798,7 +798,7 @@
         <v>130184920</v>
       </c>
       <c r="B3" t="n">
-        <v>80154</v>
+        <v>80180</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>

--- a/artfynd/A 54167-2025 artfynd.xlsx
+++ b/artfynd/A 54167-2025 artfynd.xlsx
@@ -798,7 +798,7 @@
         <v>130184920</v>
       </c>
       <c r="B3" t="n">
-        <v>80180</v>
+        <v>80182</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>

--- a/artfynd/A 54167-2025 artfynd.xlsx
+++ b/artfynd/A 54167-2025 artfynd.xlsx
@@ -675,15 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>73616849</v>
+        <v>130184920</v>
       </c>
       <c r="B2" t="n">
-        <v>78569</v>
-      </c>
-      <c r="C2" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>80298</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -691,39 +686,37 @@
         </is>
       </c>
       <c r="E2" t="n">
-        <v>6458</v>
+        <v>388</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Stiftgelélav</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Collema furfuraceum</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Arnold) Du Rietz</t>
         </is>
       </c>
       <c r="I2" t="inlineStr"/>
-      <c r="J2" t="inlineStr"/>
-      <c r="K2" t="inlineStr"/>
       <c r="P2" t="inlineStr">
         <is>
-          <t>Björkbergsmyran, Björkberget, Nb</t>
+          <t>Haparanda-Boden, Nb</t>
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>807941.4362151907</v>
+        <v>807942</v>
       </c>
       <c r="R2" t="n">
-        <v>7325026.709488356</v>
+        <v>7325059</v>
       </c>
       <c r="S2" t="n">
-        <v>50</v>
+        <v>10</v>
       </c>
       <c r="T2" t="inlineStr">
         <is>
@@ -747,27 +740,27 @@
       </c>
       <c r="Y2" t="inlineStr">
         <is>
-          <t>2018-10-18</t>
+          <t>2025-09-01</t>
         </is>
       </c>
       <c r="Z2" t="inlineStr">
         <is>
-          <t>09:30</t>
+          <t>08:20</t>
         </is>
       </c>
       <c r="AA2" t="inlineStr">
         <is>
-          <t>2018-10-18</t>
+          <t>2025-09-01</t>
         </is>
       </c>
       <c r="AB2" t="inlineStr">
         <is>
-          <t>09:30</t>
+          <t>08:20</t>
         </is>
       </c>
       <c r="AC2" t="inlineStr">
         <is>
-          <t>En sälg intill vägen.</t>
+          <t>NVI (C250260) Calluna AB</t>
         </is>
       </c>
       <c r="AD2" t="b">
@@ -776,29 +769,28 @@
       <c r="AE2" t="b">
         <v>0</v>
       </c>
-      <c r="AF2" t="inlineStr"/>
       <c r="AG2" t="b">
         <v>0</v>
       </c>
       <c r="AT2" t="inlineStr"/>
       <c r="AW2" t="inlineStr">
         <is>
-          <t>Mats Bergquist</t>
+          <t>Jonas Mattsson</t>
         </is>
       </c>
       <c r="AX2" t="inlineStr">
         <is>
-          <t>Mats Bergquist, Berth-Ove Lindström</t>
+          <t>Josefina Pehrson</t>
         </is>
       </c>
       <c r="AY2" t="inlineStr"/>
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>130184920</v>
+        <v>73616849</v>
       </c>
       <c r="B3" t="n">
-        <v>80182</v>
+        <v>80432</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -806,37 +798,39 @@
         </is>
       </c>
       <c r="E3" t="n">
-        <v>388</v>
+        <v>6458</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Stiftgelélav</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Collema furfuraceum</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(Arnold) Du Rietz</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I3" t="inlineStr"/>
+      <c r="J3" t="inlineStr"/>
+      <c r="K3" t="inlineStr"/>
       <c r="P3" t="inlineStr">
         <is>
-          <t>Haparanda-Boden, Nb</t>
+          <t>Björkbergsmyran, Björkberget, Nb</t>
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>807942</v>
+        <v>807941</v>
       </c>
       <c r="R3" t="n">
-        <v>7325059</v>
+        <v>7325027</v>
       </c>
       <c r="S3" t="n">
-        <v>10</v>
+        <v>50</v>
       </c>
       <c r="T3" t="inlineStr">
         <is>
@@ -860,27 +854,27 @@
       </c>
       <c r="Y3" t="inlineStr">
         <is>
-          <t>2025-09-01</t>
+          <t>2018-10-18</t>
         </is>
       </c>
       <c r="Z3" t="inlineStr">
         <is>
-          <t>08:20</t>
+          <t>09:30</t>
         </is>
       </c>
       <c r="AA3" t="inlineStr">
         <is>
-          <t>2025-09-01</t>
+          <t>2018-10-18</t>
         </is>
       </c>
       <c r="AB3" t="inlineStr">
         <is>
-          <t>08:20</t>
+          <t>09:30</t>
         </is>
       </c>
       <c r="AC3" t="inlineStr">
         <is>
-          <t>NVI (C250260) Calluna AB</t>
+          <t>En sälg intill vägen.</t>
         </is>
       </c>
       <c r="AD3" t="b">
@@ -889,18 +883,19 @@
       <c r="AE3" t="b">
         <v>0</v>
       </c>
+      <c r="AF3" t="inlineStr"/>
       <c r="AG3" t="b">
         <v>0</v>
       </c>
       <c r="AT3" t="inlineStr"/>
       <c r="AW3" t="inlineStr">
         <is>
-          <t>Jonas Mattsson</t>
+          <t>Mats Bergquist</t>
         </is>
       </c>
       <c r="AX3" t="inlineStr">
         <is>
-          <t>Josefina Pehrson</t>
+          <t>Mats Bergquist, Berth-Ove Lindström</t>
         </is>
       </c>
       <c r="AY3" t="inlineStr"/>

--- a/artfynd/A 54167-2025 artfynd.xlsx
+++ b/artfynd/A 54167-2025 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY3"/>
+  <dimension ref="A1:AZ3"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -672,6 +672,11 @@
           <t>Projektnamn</t>
         </is>
       </c>
+      <c r="AZ1" t="inlineStr">
+        <is>
+          <t>Artportalenlänk</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" t="n">
@@ -784,6 +789,11 @@
         </is>
       </c>
       <c r="AY2" t="inlineStr"/>
+      <c r="AZ2" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/130184920</t>
+        </is>
+      </c>
     </row>
     <row r="3">
       <c r="A3" t="n">
@@ -899,8 +909,17 @@
         </is>
       </c>
       <c r="AY3" t="inlineStr"/>
+      <c r="AZ3" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/73616849</t>
+        </is>
+      </c>
     </row>
   </sheetData>
+  <hyperlinks>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ2" r:id="rId1"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ3" r:id="rId2"/>
+  </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>
--- a/artfynd/A 54167-2025 artfynd.xlsx
+++ b/artfynd/A 54167-2025 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AZ3"/>
+  <dimension ref="A1:AZ6"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -912,6 +912,385 @@
       <c r="AZ3" t="inlineStr">
         <is>
           <t>https://artportalen.se/Sighting/73616849</t>
+        </is>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" t="n">
+        <v>136155783</v>
+      </c>
+      <c r="B4" t="n">
+        <v>57979</v>
+      </c>
+      <c r="D4" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E4" t="n">
+        <v>100049</v>
+      </c>
+      <c r="F4" t="inlineStr">
+        <is>
+          <t>Spillkråka</t>
+        </is>
+      </c>
+      <c r="G4" t="inlineStr">
+        <is>
+          <t>Dryocopus martius</t>
+        </is>
+      </c>
+      <c r="H4" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I4" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="K4" t="inlineStr"/>
+      <c r="L4" t="inlineStr"/>
+      <c r="M4" t="inlineStr">
+        <is>
+          <t>födosökande</t>
+        </is>
+      </c>
+      <c r="N4" t="inlineStr"/>
+      <c r="P4" t="inlineStr">
+        <is>
+          <t>Björkbergsmyran, Björkberget, Nb</t>
+        </is>
+      </c>
+      <c r="Q4" t="n">
+        <v>807941</v>
+      </c>
+      <c r="R4" t="n">
+        <v>7325027</v>
+      </c>
+      <c r="S4" t="n">
+        <v>50</v>
+      </c>
+      <c r="T4" t="inlineStr">
+        <is>
+          <t>Norrbotten</t>
+        </is>
+      </c>
+      <c r="U4" t="inlineStr">
+        <is>
+          <t>Boden</t>
+        </is>
+      </c>
+      <c r="V4" t="inlineStr">
+        <is>
+          <t>Norrbotten</t>
+        </is>
+      </c>
+      <c r="W4" t="inlineStr">
+        <is>
+          <t>Överluleå</t>
+        </is>
+      </c>
+      <c r="Y4" t="inlineStr">
+        <is>
+          <t>2026-08-26</t>
+        </is>
+      </c>
+      <c r="Z4" t="inlineStr">
+        <is>
+          <t>14:10</t>
+        </is>
+      </c>
+      <c r="AA4" t="inlineStr">
+        <is>
+          <t>2026-08-26</t>
+        </is>
+      </c>
+      <c r="AB4" t="inlineStr">
+        <is>
+          <t>15:35</t>
+        </is>
+      </c>
+      <c r="AD4" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE4" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG4" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT4" t="inlineStr"/>
+      <c r="AW4" t="inlineStr">
+        <is>
+          <t>Mats Bergquist</t>
+        </is>
+      </c>
+      <c r="AX4" t="inlineStr">
+        <is>
+          <t>Mats Bergquist</t>
+        </is>
+      </c>
+      <c r="AY4" t="inlineStr"/>
+      <c r="AZ4" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/136155783</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" t="n">
+        <v>136155786</v>
+      </c>
+      <c r="B5" t="n">
+        <v>57160</v>
+      </c>
+      <c r="D5" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E5" t="n">
+        <v>102612</v>
+      </c>
+      <c r="F5" t="inlineStr">
+        <is>
+          <t>Järpe</t>
+        </is>
+      </c>
+      <c r="G5" t="inlineStr">
+        <is>
+          <t>Tetrastes bonasia</t>
+        </is>
+      </c>
+      <c r="H5" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I5" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="K5" t="inlineStr"/>
+      <c r="L5" t="inlineStr"/>
+      <c r="M5" t="inlineStr">
+        <is>
+          <t>födosökande</t>
+        </is>
+      </c>
+      <c r="N5" t="inlineStr"/>
+      <c r="P5" t="inlineStr">
+        <is>
+          <t>Björkbergsmyran, Björkberget, Nb</t>
+        </is>
+      </c>
+      <c r="Q5" t="n">
+        <v>807941</v>
+      </c>
+      <c r="R5" t="n">
+        <v>7325027</v>
+      </c>
+      <c r="S5" t="n">
+        <v>50</v>
+      </c>
+      <c r="T5" t="inlineStr">
+        <is>
+          <t>Norrbotten</t>
+        </is>
+      </c>
+      <c r="U5" t="inlineStr">
+        <is>
+          <t>Boden</t>
+        </is>
+      </c>
+      <c r="V5" t="inlineStr">
+        <is>
+          <t>Norrbotten</t>
+        </is>
+      </c>
+      <c r="W5" t="inlineStr">
+        <is>
+          <t>Överluleå</t>
+        </is>
+      </c>
+      <c r="Y5" t="inlineStr">
+        <is>
+          <t>2026-08-26</t>
+        </is>
+      </c>
+      <c r="Z5" t="inlineStr">
+        <is>
+          <t>14:10</t>
+        </is>
+      </c>
+      <c r="AA5" t="inlineStr">
+        <is>
+          <t>2026-08-26</t>
+        </is>
+      </c>
+      <c r="AB5" t="inlineStr">
+        <is>
+          <t>15:35</t>
+        </is>
+      </c>
+      <c r="AD5" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE5" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG5" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT5" t="inlineStr"/>
+      <c r="AW5" t="inlineStr">
+        <is>
+          <t>Mats Bergquist</t>
+        </is>
+      </c>
+      <c r="AX5" t="inlineStr">
+        <is>
+          <t>Mats Bergquist</t>
+        </is>
+      </c>
+      <c r="AY5" t="inlineStr"/>
+      <c r="AZ5" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/136155786</t>
+        </is>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" t="n">
+        <v>136155806</v>
+      </c>
+      <c r="B6" t="n">
+        <v>58819</v>
+      </c>
+      <c r="D6" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E6" t="n">
+        <v>208245</v>
+      </c>
+      <c r="F6" t="inlineStr">
+        <is>
+          <t>Vanlig padda</t>
+        </is>
+      </c>
+      <c r="G6" t="inlineStr">
+        <is>
+          <t>Bufo bufo</t>
+        </is>
+      </c>
+      <c r="H6" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I6" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="J6" t="inlineStr"/>
+      <c r="K6" t="inlineStr"/>
+      <c r="L6" t="inlineStr"/>
+      <c r="M6" t="inlineStr">
+        <is>
+          <t>trafikdödad</t>
+        </is>
+      </c>
+      <c r="N6" t="inlineStr"/>
+      <c r="P6" t="inlineStr">
+        <is>
+          <t>Björkbergsmyran, Björkberget, Nb</t>
+        </is>
+      </c>
+      <c r="Q6" t="n">
+        <v>807941</v>
+      </c>
+      <c r="R6" t="n">
+        <v>7325027</v>
+      </c>
+      <c r="S6" t="n">
+        <v>50</v>
+      </c>
+      <c r="T6" t="inlineStr">
+        <is>
+          <t>Norrbotten</t>
+        </is>
+      </c>
+      <c r="U6" t="inlineStr">
+        <is>
+          <t>Boden</t>
+        </is>
+      </c>
+      <c r="V6" t="inlineStr">
+        <is>
+          <t>Norrbotten</t>
+        </is>
+      </c>
+      <c r="W6" t="inlineStr">
+        <is>
+          <t>Överluleå</t>
+        </is>
+      </c>
+      <c r="Y6" t="inlineStr">
+        <is>
+          <t>2026-08-26</t>
+        </is>
+      </c>
+      <c r="Z6" t="inlineStr">
+        <is>
+          <t>14:10</t>
+        </is>
+      </c>
+      <c r="AA6" t="inlineStr">
+        <is>
+          <t>2026-08-26</t>
+        </is>
+      </c>
+      <c r="AB6" t="inlineStr">
+        <is>
+          <t>15:35</t>
+        </is>
+      </c>
+      <c r="AC6" t="inlineStr">
+        <is>
+          <t>Otroligt nog är den överkörd på denna väg, där det passerar en bil i månaden!</t>
+        </is>
+      </c>
+      <c r="AD6" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE6" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF6" t="inlineStr"/>
+      <c r="AG6" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT6" t="inlineStr"/>
+      <c r="AW6" t="inlineStr">
+        <is>
+          <t>Mats Bergquist</t>
+        </is>
+      </c>
+      <c r="AX6" t="inlineStr">
+        <is>
+          <t>Mats Bergquist</t>
+        </is>
+      </c>
+      <c r="AY6" t="inlineStr"/>
+      <c r="AZ6" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/136155806</t>
         </is>
       </c>
     </row>
@@ -919,6 +1298,9 @@
   <hyperlinks>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ2" r:id="rId1"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ3" r:id="rId2"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ4" r:id="rId3"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ5" r:id="rId4"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ6" r:id="rId5"/>
   </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/artfynd/A 54167-2025 artfynd.xlsx
+++ b/artfynd/A 54167-2025 artfynd.xlsx
@@ -920,7 +920,7 @@
         <v>136155783</v>
       </c>
       <c r="B4" t="n">
-        <v>57979</v>
+        <v>57980</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -1044,7 +1044,7 @@
         <v>136155786</v>
       </c>
       <c r="B5" t="n">
-        <v>57160</v>
+        <v>57161</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1168,7 +1168,7 @@
         <v>136155806</v>
       </c>
       <c r="B6" t="n">
-        <v>58819</v>
+        <v>58820</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>

--- a/artfynd/A 54167-2025 artfynd.xlsx
+++ b/artfynd/A 54167-2025 artfynd.xlsx
@@ -920,7 +920,7 @@
         <v>136155783</v>
       </c>
       <c r="B4" t="n">
-        <v>57980</v>
+        <v>57984</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -1044,7 +1044,7 @@
         <v>136155786</v>
       </c>
       <c r="B5" t="n">
-        <v>57161</v>
+        <v>57165</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1168,7 +1168,7 @@
         <v>136155806</v>
       </c>
       <c r="B6" t="n">
-        <v>58820</v>
+        <v>58824</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>

--- a/artfynd/A 54167-2025 artfynd.xlsx
+++ b/artfynd/A 54167-2025 artfynd.xlsx
@@ -920,7 +920,7 @@
         <v>136155783</v>
       </c>
       <c r="B4" t="n">
-        <v>57984</v>
+        <v>57985</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -1044,7 +1044,7 @@
         <v>136155786</v>
       </c>
       <c r="B5" t="n">
-        <v>57165</v>
+        <v>57166</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1168,7 +1168,7 @@
         <v>136155806</v>
       </c>
       <c r="B6" t="n">
-        <v>58824</v>
+        <v>58825</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>

--- a/artfynd/A 54167-2025 artfynd.xlsx
+++ b/artfynd/A 54167-2025 artfynd.xlsx
@@ -920,7 +920,7 @@
         <v>136155783</v>
       </c>
       <c r="B4" t="n">
-        <v>57985</v>
+        <v>57990</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -1044,7 +1044,7 @@
         <v>136155786</v>
       </c>
       <c r="B5" t="n">
-        <v>57166</v>
+        <v>57171</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1168,7 +1168,7 @@
         <v>136155806</v>
       </c>
       <c r="B6" t="n">
-        <v>58825</v>
+        <v>58830</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>

--- a/artfynd/A 54167-2025 artfynd.xlsx
+++ b/artfynd/A 54167-2025 artfynd.xlsx
@@ -920,7 +920,7 @@
         <v>136155783</v>
       </c>
       <c r="B4" t="n">
-        <v>57990</v>
+        <v>58003</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -1044,7 +1044,7 @@
         <v>136155786</v>
       </c>
       <c r="B5" t="n">
-        <v>57171</v>
+        <v>57184</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1168,7 +1168,7 @@
         <v>136155806</v>
       </c>
       <c r="B6" t="n">
-        <v>58830</v>
+        <v>58843</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
